--- a/data/trans_orig/DC_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/DC_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico (incluye Otro dolor crónico) en 2023</t>
+          <t>Población con dolor crónico (incluye Otro dolor crónico) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78319</t>
+          <t>78170</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113498</t>
+          <t>111641</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>139812</t>
+          <t>139104</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>174470</t>
+          <t>172645</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>224789</t>
+          <t>223136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>276533</t>
+          <t>275231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>391714</t>
+          <t>393571</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426893</t>
+          <t>427042</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272997</t>
+          <t>274822</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>307655</t>
+          <t>308363</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>676146</t>
+          <t>677448</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>727890</t>
+          <t>729543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72613</t>
+          <t>73812</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106768</t>
+          <t>105061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125674</t>
+          <t>127937</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160105</t>
+          <t>159373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>207055</t>
+          <t>206899</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>255798</t>
+          <t>255040</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345445</t>
+          <t>347152</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>379600</t>
+          <t>378401</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>222475</t>
+          <t>223207</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>256906</t>
+          <t>254643</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>578995</t>
+          <t>579753</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>627738</t>
+          <t>627894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,22%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39225</t>
+          <t>46928</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>194609</t>
+          <t>193563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69589</t>
+          <t>69279</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89791</t>
+          <t>89123</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86560</t>
+          <t>91924</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>285511</t>
+          <t>281808</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,74%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>473655</t>
+          <t>474701</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629039</t>
+          <t>621336</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77120</t>
+          <t>77788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97322</t>
+          <t>97632</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>549664</t>
+          <t>553367</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>748615</t>
+          <t>743251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>249895</t>
+          <t>250091</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>305476</t>
+          <t>309099</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>357135</t>
+          <t>357372</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>726178</t>
+          <t>691471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>620010</t>
+          <t>617297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1122357</t>
+          <t>1173967</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>58,32%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>729343</t>
+          <t>725720</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>784924</t>
+          <t>784728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>251916</t>
+          <t>286623</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>620959</t>
+          <t>620722</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>890555</t>
+          <t>838945</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1392902</t>
+          <t>1395615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,33%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107793</t>
+          <t>108411</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147267</t>
+          <t>147254</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>379674</t>
+          <t>380424</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>539066</t>
+          <t>534236</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>496407</t>
+          <t>497986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>687841</t>
+          <t>683908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>51,95%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>327779</t>
+          <t>327792</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>367253</t>
+          <t>366635</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>302269</t>
+          <t>307099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>461661</t>
+          <t>460911</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>628540</t>
+          <t>632473</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>819974</t>
+          <t>818395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,17%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14339</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45985</t>
+          <t>45843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>270315</t>
+          <t>270428</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>317286</t>
+          <t>316979</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>290975</t>
+          <t>290832</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>348812</t>
+          <t>352952</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194522</t>
+          <t>194664</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226168</t>
+          <t>227170</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>444085</t>
+          <t>444392</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>491056</t>
+          <t>490943</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>653066</t>
+          <t>648926</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>710903</t>
+          <t>711046</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,97%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>577273</t>
+          <t>575667</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>801170</t>
+          <t>801587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1448714</t>
+          <t>1438371</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2031324</t>
+          <t>1940187</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2089952</t>
+          <t>2091030</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2825273</t>
+          <t>2778251</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2574890</t>
+          <t>2574473</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2798787</t>
+          <t>2800393</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1546434</t>
+          <t>1637571</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2129044</t>
+          <t>2139387</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4128545</t>
+          <t>4175567</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4863866</t>
+          <t>4862788</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DC_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/DC_R-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>93889</t>
+          <t>103099</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78170</t>
+          <t>86336</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111641</t>
+          <t>121954</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>156423</t>
+          <t>171920</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>139104</t>
+          <t>153952</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>172645</t>
+          <t>192007</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>250312</t>
+          <t>275019</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>223136</t>
+          <t>250907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>275231</t>
+          <t>302018</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>411323</t>
+          <t>447519</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393571</t>
+          <t>428664</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427042</t>
+          <t>464282</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>291044</t>
+          <t>316491</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274822</t>
+          <t>296404</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308363</t>
+          <t>334459</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>702367</t>
+          <t>764010</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>677448</t>
+          <t>737011</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>729543</t>
+          <t>788122</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>75,85%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88800</t>
+          <t>93409</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73812</t>
+          <t>76698</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105061</t>
+          <t>109810</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>142406</t>
+          <t>161647</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>127937</t>
+          <t>145430</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>159373</t>
+          <t>180251</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>231206</t>
+          <t>255056</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>206899</t>
+          <t>231276</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>255040</t>
+          <t>284090</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>363413</t>
+          <t>389803</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>347152</t>
+          <t>373402</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>378401</t>
+          <t>406514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>240174</t>
+          <t>261496</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>223207</t>
+          <t>242892</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>254643</t>
+          <t>277713</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>603587</t>
+          <t>651299</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>579753</t>
+          <t>622265</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>627894</t>
+          <t>675079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>74,48%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>116923</t>
+          <t>128428</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46928</t>
+          <t>108637</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>193563</t>
+          <t>148242</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>79769</t>
+          <t>89955</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69279</t>
+          <t>78774</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89123</t>
+          <t>100707</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>196691</t>
+          <t>218384</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91924</t>
+          <t>196030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>281808</t>
+          <t>240660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>551341</t>
+          <t>343184</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>474701</t>
+          <t>323370</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621336</t>
+          <t>362975</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87142</t>
+          <t>97542</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77788</t>
+          <t>86790</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97632</t>
+          <t>108723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>638484</t>
+          <t>440725</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>553367</t>
+          <t>418449</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>743251</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>70,26%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>275632</t>
+          <t>293722</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>250091</t>
+          <t>264642</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>309099</t>
+          <t>327202</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>496495</t>
+          <t>328944</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>357372</t>
+          <t>305373</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>691471</t>
+          <t>354362</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>772126</t>
+          <t>622665</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>617297</t>
+          <t>584373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1173967</t>
+          <t>660447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>759187</t>
+          <t>838121</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>725720</t>
+          <t>804641</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>784728</t>
+          <t>867201</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>481599</t>
+          <t>532267</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>286623</t>
+          <t>506849</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>620722</t>
+          <t>555838</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1240786</t>
+          <t>1370389</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>838945</t>
+          <t>1332607</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1395615</t>
+          <t>1408681</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>126343</t>
+          <t>143331</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>108411</t>
+          <t>123266</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147254</t>
+          <t>166611</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>431613</t>
+          <t>399564</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>380424</t>
+          <t>376154</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>534236</t>
+          <t>423185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>557956</t>
+          <t>542895</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>497986</t>
+          <t>511708</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>683908</t>
+          <t>579815</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>41,45%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>348703</t>
+          <t>424633</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>327792</t>
+          <t>401353</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>366635</t>
+          <t>444698</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>409722</t>
+          <t>431286</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>307099</t>
+          <t>407665</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>460911</t>
+          <t>454696</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>758425</t>
+          <t>855919</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>632473</t>
+          <t>818999</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>818395</t>
+          <t>887106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>63,42%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25989</t>
+          <t>25693</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13337</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45843</t>
+          <t>43298</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>294322</t>
+          <t>322428</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>270428</t>
+          <t>297624</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>316979</t>
+          <t>350627</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>320311</t>
+          <t>348121</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>290832</t>
+          <t>316089</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>352952</t>
+          <t>380327</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>214518</t>
+          <t>211535</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194664</t>
+          <t>193930</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>227170</t>
+          <t>222194</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>467049</t>
+          <t>521853</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>444392</t>
+          <t>493654</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>490943</t>
+          <t>546657</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>681567</t>
+          <t>733388</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>648926</t>
+          <t>701182</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>711046</t>
+          <t>765420</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,77%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>727576</t>
+          <t>787682</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>575667</t>
+          <t>737161</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>801587</t>
+          <t>843371</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1601027</t>
+          <t>1474457</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1438371</t>
+          <t>1420303</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1940187</t>
+          <t>1523550</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2328603</t>
+          <t>2262139</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2091030</t>
+          <t>2186176</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2778251</t>
+          <t>2332468</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2648484</t>
+          <t>2654794</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2574473</t>
+          <t>2599105</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2800393</t>
+          <t>2705315</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1976731</t>
+          <t>2160936</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1637571</t>
+          <t>2111843</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2139387</t>
+          <t>2215090</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4625215</t>
+          <t>4815730</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4175567</t>
+          <t>4745401</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4862788</t>
+          <t>4891693</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
